--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132050911</v>
+        <v>132050923</v>
       </c>
       <c r="B2" t="n">
-        <v>57906</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480173</v>
+        <v>479893</v>
       </c>
       <c r="R2" t="n">
-        <v>6991957</v>
+        <v>6992693</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132050906</v>
+        <v>132050911</v>
       </c>
       <c r="B3" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480160</v>
+        <v>480173</v>
       </c>
       <c r="R3" t="n">
-        <v>6992030</v>
+        <v>6991957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050923</v>
+        <v>132050906</v>
       </c>
       <c r="B4" t="n">
-        <v>79268</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479893</v>
+        <v>480160</v>
       </c>
       <c r="R4" t="n">
-        <v>6992693</v>
+        <v>6992030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,12 +939,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>132050902</v>
       </c>
       <c r="B5" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050915</v>
+        <v>132050894</v>
       </c>
       <c r="B6" t="n">
-        <v>57906</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480194</v>
+        <v>479925</v>
       </c>
       <c r="R6" t="n">
-        <v>6991909</v>
+        <v>6992644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,17 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050894</v>
+        <v>132050915</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479925</v>
+        <v>480194</v>
       </c>
       <c r="R7" t="n">
-        <v>6992644</v>
+        <v>6991909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1240,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>132050903</v>
       </c>
       <c r="B8" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132050899</v>
       </c>
       <c r="B9" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>132050908</v>
       </c>
       <c r="B10" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050912</v>
+        <v>132050909</v>
       </c>
       <c r="B11" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480211</v>
+        <v>480164</v>
       </c>
       <c r="R11" t="n">
-        <v>6991929</v>
+        <v>6991987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack,  färska och äldre, på gran</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050909</v>
+        <v>132050912</v>
       </c>
       <c r="B12" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480164</v>
+        <v>480211</v>
       </c>
       <c r="R12" t="n">
-        <v>6991987</v>
+        <v>6991929</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>Ringhack,  färska och äldre, på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1790,7 @@
         <v>132050901</v>
       </c>
       <c r="B13" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>132050917</v>
       </c>
       <c r="B14" t="n">
-        <v>80402</v>
+        <v>80403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>132050924</v>
       </c>
       <c r="B15" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>132050905</v>
       </c>
       <c r="B16" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>132050927</v>
       </c>
       <c r="B17" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132050921</v>
+        <v>132050925</v>
       </c>
       <c r="B18" t="n">
-        <v>99046</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479902</v>
+        <v>479991</v>
       </c>
       <c r="R18" t="n">
-        <v>6992715</v>
+        <v>6992628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132050925</v>
+        <v>132050921</v>
       </c>
       <c r="B19" t="n">
-        <v>79268</v>
+        <v>99047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2424,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479991</v>
+        <v>479902</v>
       </c>
       <c r="R19" t="n">
-        <v>6992628</v>
+        <v>6992715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2460,6 +2455,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2489,7 +2489,7 @@
         <v>132050893</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>132050898</v>
       </c>
       <c r="B21" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>132050920</v>
       </c>
       <c r="B22" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>132050913</v>
       </c>
       <c r="B23" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>132050914</v>
       </c>
       <c r="B24" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>132050904</v>
       </c>
       <c r="B25" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>132050919</v>
       </c>
       <c r="B26" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>132050900</v>
       </c>
       <c r="B27" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>132050907</v>
       </c>
       <c r="B28" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050923</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050911</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050906</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132050902</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132050894</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132050915</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132050903</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132050899</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>132050908</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>132050909</v>
       </c>
       <c r="B11" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>132050912</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>132050901</v>
       </c>
       <c r="B13" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050917</v>
+        <v>132050924</v>
       </c>
       <c r="B14" t="n">
-        <v>80403</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479910</v>
+        <v>479913</v>
       </c>
       <c r="R14" t="n">
-        <v>6992762</v>
+        <v>6992744</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050924</v>
+        <v>132050917</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>80408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479913</v>
+        <v>479910</v>
       </c>
       <c r="R15" t="n">
-        <v>6992744</v>
+        <v>6992762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
         <v>132050905</v>
       </c>
       <c r="B16" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>132050927</v>
       </c>
       <c r="B17" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>132050925</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>132050921</v>
       </c>
       <c r="B19" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>132050893</v>
       </c>
       <c r="B20" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>132050898</v>
       </c>
       <c r="B21" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>132050920</v>
       </c>
       <c r="B22" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>132050913</v>
       </c>
       <c r="B23" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>132050914</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>132050904</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>132050919</v>
       </c>
       <c r="B26" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>132050900</v>
       </c>
       <c r="B27" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>132050907</v>
       </c>
       <c r="B28" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050894</v>
+        <v>132050915</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>57912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479925</v>
+        <v>480194</v>
       </c>
       <c r="R6" t="n">
-        <v>6992644</v>
+        <v>6991909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,12 +1143,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050915</v>
+        <v>132050894</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>91846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480194</v>
+        <v>479925</v>
       </c>
       <c r="R7" t="n">
-        <v>6991909</v>
+        <v>6992644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,17 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1889,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050924</v>
+        <v>132050917</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>80408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479913</v>
+        <v>479910</v>
       </c>
       <c r="R14" t="n">
-        <v>6992744</v>
+        <v>6992762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050917</v>
+        <v>132050924</v>
       </c>
       <c r="B15" t="n">
-        <v>80408</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479910</v>
+        <v>479913</v>
       </c>
       <c r="R15" t="n">
-        <v>6992762</v>
+        <v>6992744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050923</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050911</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050906</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132050902</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050915</v>
+        <v>132050894</v>
       </c>
       <c r="B6" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480194</v>
+        <v>479925</v>
       </c>
       <c r="R6" t="n">
-        <v>6991909</v>
+        <v>6992644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,17 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050894</v>
+        <v>132050915</v>
       </c>
       <c r="B7" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479925</v>
+        <v>480194</v>
       </c>
       <c r="R7" t="n">
-        <v>6992644</v>
+        <v>6991909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1240,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>132050903</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132050899</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050908</v>
+        <v>132050912</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480129</v>
+        <v>480211</v>
       </c>
       <c r="R10" t="n">
-        <v>6992035</v>
+        <v>6991929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>Ringhack,  färska och äldre, på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,7 +1586,7 @@
         <v>132050909</v>
       </c>
       <c r="B11" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050912</v>
+        <v>132050908</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480211</v>
+        <v>480129</v>
       </c>
       <c r="R12" t="n">
-        <v>6991929</v>
+        <v>6992035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack,  färska och äldre, på gran</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,7 +1790,7 @@
         <v>132050901</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>132050917</v>
       </c>
       <c r="B14" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>132050924</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>132050905</v>
       </c>
       <c r="B16" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>132050927</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>132050925</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>132050921</v>
       </c>
       <c r="B19" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132050893</v>
+        <v>132050898</v>
       </c>
       <c r="B20" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479995</v>
+        <v>479999</v>
       </c>
       <c r="R20" t="n">
-        <v>6992593</v>
+        <v>6992754</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,12 +2551,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132050898</v>
+        <v>132050893</v>
       </c>
       <c r="B21" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479999</v>
+        <v>479995</v>
       </c>
       <c r="R21" t="n">
-        <v>6992754</v>
+        <v>6992593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,17 +2653,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2688,7 +2688,7 @@
         <v>132050920</v>
       </c>
       <c r="B22" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>132050913</v>
       </c>
       <c r="B23" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132050914</v>
+        <v>132050904</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480191</v>
+        <v>480194</v>
       </c>
       <c r="R24" t="n">
-        <v>6991908</v>
+        <v>6992012</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132050904</v>
+        <v>132050914</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480194</v>
+        <v>480191</v>
       </c>
       <c r="R25" t="n">
-        <v>6992012</v>
+        <v>6991908</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3096,7 +3096,7 @@
         <v>132050919</v>
       </c>
       <c r="B26" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>132050900</v>
       </c>
       <c r="B27" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>132050907</v>
       </c>
       <c r="B28" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132050911</v>
+        <v>132616047</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480173</v>
+        <v>480116</v>
       </c>
       <c r="R2" t="n">
-        <v>6991957</v>
+        <v>6992294</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132050906</v>
+        <v>132616090</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>92689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480160</v>
+        <v>480161</v>
       </c>
       <c r="R3" t="n">
-        <v>6992030</v>
+        <v>6992052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050923</v>
+        <v>132616084</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479893</v>
+        <v>480141</v>
       </c>
       <c r="R4" t="n">
-        <v>6992693</v>
+        <v>6992268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050902</v>
+        <v>132050893</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480196</v>
+        <v>479995</v>
       </c>
       <c r="R5" t="n">
-        <v>6991998</v>
+        <v>6992593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050915</v>
+        <v>132050894</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480194</v>
+        <v>479925</v>
       </c>
       <c r="R6" t="n">
-        <v>6991909</v>
+        <v>6992644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050894</v>
+        <v>132616030</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479925</v>
+        <v>480166</v>
       </c>
       <c r="R7" t="n">
-        <v>6992644</v>
+        <v>6992072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132050903</v>
+        <v>132616031</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480196</v>
+        <v>480167</v>
       </c>
       <c r="R8" t="n">
-        <v>6992003</v>
+        <v>6992137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,17 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132050899</v>
+        <v>132616033</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480057</v>
+        <v>480118</v>
       </c>
       <c r="R9" t="n">
-        <v>6992159</v>
+        <v>6992213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på tall</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050908</v>
+        <v>132616034</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480129</v>
+        <v>480114</v>
       </c>
       <c r="R10" t="n">
-        <v>6992035</v>
+        <v>6992295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050909</v>
+        <v>132616035</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480164</v>
+        <v>480020</v>
       </c>
       <c r="R11" t="n">
-        <v>6991987</v>
+        <v>6992679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,17 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050912</v>
+        <v>132616036</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480211</v>
+        <v>479905</v>
       </c>
       <c r="R12" t="n">
-        <v>6991929</v>
+        <v>6992806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,17 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack,  färska och äldre, på gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050901</v>
+        <v>132050923</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480106</v>
+        <v>479893</v>
       </c>
       <c r="R13" t="n">
-        <v>6992094</v>
+        <v>6992693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,17 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på tall</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050917</v>
+        <v>132050924</v>
       </c>
       <c r="B14" t="n">
-        <v>80461</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479910</v>
+        <v>479913</v>
       </c>
       <c r="R14" t="n">
-        <v>6992762</v>
+        <v>6992744</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050924</v>
+        <v>132050925</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2021,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479913</v>
+        <v>479991</v>
       </c>
       <c r="R15" t="n">
-        <v>6992744</v>
+        <v>6992628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132050905</v>
+        <v>132050927</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480192</v>
+        <v>480169</v>
       </c>
       <c r="R16" t="n">
-        <v>6992019</v>
+        <v>6991964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2108,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,14 +2135,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132050927</v>
+        <v>132616088</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2216,14 +2166,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480169</v>
+        <v>480021</v>
       </c>
       <c r="R17" t="n">
-        <v>6991964</v>
+        <v>6992811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2250,17 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132050921</v>
+        <v>132616089</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,34 +2243,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479902</v>
+        <v>480031</v>
       </c>
       <c r="R18" t="n">
-        <v>6992715</v>
+        <v>6992700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,17 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 plantor</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132050925</v>
+        <v>132616028</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2400,34 +2340,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479991</v>
+        <v>479938</v>
       </c>
       <c r="R19" t="n">
-        <v>6992628</v>
+        <v>6992708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132050893</v>
+        <v>132616029</v>
       </c>
       <c r="B20" t="n">
-        <v>91909</v>
+        <v>83358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,34 +2437,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479995</v>
+        <v>480053</v>
       </c>
       <c r="R20" t="n">
-        <v>6992593</v>
+        <v>6992722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132050898</v>
+        <v>132050917</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>80493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479999</v>
+        <v>479910</v>
       </c>
       <c r="R21" t="n">
-        <v>6992754</v>
+        <v>6992762</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,17 +2588,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,45 +2620,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132050920</v>
+        <v>132616044</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>80493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479905</v>
+        <v>480144</v>
       </c>
       <c r="R22" t="n">
-        <v>6992663</v>
+        <v>6992112</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,17 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>4st plantor, utspridda sporadiskt</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,45 +2717,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132050913</v>
+        <v>132616045</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>80493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480209</v>
+        <v>480012</v>
       </c>
       <c r="R23" t="n">
-        <v>6991932</v>
+        <v>6992800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,17 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,27 +2814,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132050914</v>
+        <v>132616046</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2920,14 +2845,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480191</v>
+        <v>480120</v>
       </c>
       <c r="R24" t="n">
-        <v>6991908</v>
+        <v>6992284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,17 +2879,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132050904</v>
+        <v>132050898</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480194</v>
+        <v>479999</v>
       </c>
       <c r="R25" t="n">
-        <v>6992012</v>
+        <v>6992754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,32 +3018,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132050919</v>
+        <v>132050899</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479887</v>
+        <v>480057</v>
       </c>
       <c r="R26" t="n">
-        <v>6992672</v>
+        <v>6992159</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3158,17 +3083,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2 st plantor</t>
+          <t>Ringhack, färska och äldre, på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3198,7 +3123,7 @@
         <v>132050900</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3297,10 +3222,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132050907</v>
+        <v>132050901</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3332,10 +3257,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480132</v>
+        <v>480106</v>
       </c>
       <c r="R28" t="n">
-        <v>6992053</v>
+        <v>6992094</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,7 +3297,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall</t>
+          <t>Ringhack, färska och äldre, på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3399,45 +3324,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132616074</v>
+        <v>132050902</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479936</v>
+        <v>480196</v>
       </c>
       <c r="R29" t="n">
-        <v>6992687</v>
+        <v>6991998</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3464,17 +3389,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3501,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132616033</v>
+        <v>132050903</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,34 +3437,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480118</v>
+        <v>480196</v>
       </c>
       <c r="R30" t="n">
-        <v>6992213</v>
+        <v>6992003</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,12 +3491,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3598,45 +3528,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132616051</v>
+        <v>132050904</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479998</v>
+        <v>480194</v>
       </c>
       <c r="R31" t="n">
-        <v>6992723</v>
+        <v>6992012</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,12 +3593,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3695,45 +3630,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132616072</v>
+        <v>132050905</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480002</v>
+        <v>480192</v>
       </c>
       <c r="R32" t="n">
-        <v>6992732</v>
+        <v>6992019</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,17 +3695,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50-100 plantor utspridda kluster</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3797,45 +3732,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132616090</v>
+        <v>132050906</v>
       </c>
       <c r="B33" t="n">
-        <v>92614</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480161</v>
+        <v>480160</v>
       </c>
       <c r="R33" t="n">
-        <v>6992052</v>
+        <v>6992030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,12 +3797,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3894,10 +3834,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132616047</v>
+        <v>132050907</v>
       </c>
       <c r="B34" t="n">
-        <v>92217</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3905,34 +3845,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480116</v>
+        <v>480132</v>
       </c>
       <c r="R34" t="n">
-        <v>6992294</v>
+        <v>6992053</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3959,12 +3899,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3991,45 +3936,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132616049</v>
+        <v>132050908</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480103</v>
+        <v>480129</v>
       </c>
       <c r="R35" t="n">
-        <v>6992106</v>
+        <v>6992035</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4056,17 +4001,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mer än 10 plantor</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4093,45 +4038,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132616078</v>
+        <v>132050909</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479874</v>
+        <v>480164</v>
       </c>
       <c r="R36" t="n">
-        <v>6992752</v>
+        <v>6991987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4158,17 +4103,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>4 st plantor</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4195,10 +4140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132616031</v>
+        <v>132050911</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,34 +4151,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480167</v>
+        <v>480173</v>
       </c>
       <c r="R37" t="n">
-        <v>6992137</v>
+        <v>6991957</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,12 +4205,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4292,45 +4242,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132616060</v>
+        <v>132050912</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480016</v>
+        <v>480211</v>
       </c>
       <c r="R38" t="n">
-        <v>6992696</v>
+        <v>6991929</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4357,17 +4307,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 20 st plantor</t>
+          <t>Ringhack,  färska och äldre, på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4394,10 +4344,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132616046</v>
+        <v>132050913</v>
       </c>
       <c r="B39" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4405,16 +4355,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4425,14 +4375,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480120</v>
+        <v>480209</v>
       </c>
       <c r="R39" t="n">
-        <v>6992284</v>
+        <v>6991932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4459,17 +4409,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4496,45 +4446,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132616076</v>
+        <v>132050914</v>
       </c>
       <c r="B40" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479893</v>
+        <v>480191</v>
       </c>
       <c r="R40" t="n">
-        <v>6992754</v>
+        <v>6991908</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4561,17 +4511,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Över 50 plantor, utspritt i kluster</t>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132616035</v>
+        <v>132050915</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,34 +4559,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480020</v>
+        <v>480194</v>
       </c>
       <c r="R41" t="n">
-        <v>6992679</v>
+        <v>6991909</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4663,12 +4613,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4695,10 +4650,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132616034</v>
+        <v>132616037</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4661,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480114</v>
+        <v>480166</v>
       </c>
       <c r="R42" t="n">
-        <v>6992295</v>
+        <v>6992073</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4792,32 +4752,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132616057</v>
+        <v>132616038</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480029</v>
+        <v>480165</v>
       </c>
       <c r="R43" t="n">
-        <v>6992701</v>
+        <v>6992129</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,7 +4827,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,45 +4854,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132616089</v>
+        <v>132616041</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>57162</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480031</v>
+        <v>480066</v>
       </c>
       <c r="R44" t="n">
-        <v>6992700</v>
+        <v>6992598</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4965,6 +4933,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning, tupp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4991,45 +4964,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132616044</v>
+        <v>132050919</v>
       </c>
       <c r="B45" t="n">
-        <v>80467</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480144</v>
+        <v>479887</v>
       </c>
       <c r="R45" t="n">
-        <v>6992112</v>
+        <v>6992672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,12 +5029,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 st plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5088,45 +5066,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132616088</v>
+        <v>132050920</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480021</v>
+        <v>479905</v>
       </c>
       <c r="R46" t="n">
-        <v>6992811</v>
+        <v>6992663</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5153,12 +5131,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4st plantor, utspridda sporadiskt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,10 +5168,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132616055</v>
+        <v>132050921</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,14 +5199,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480017</v>
+        <v>479902</v>
       </c>
       <c r="R47" t="n">
-        <v>6992735</v>
+        <v>6992715</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5250,17 +5233,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>6 st små plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,32 +5270,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132616029</v>
+        <v>132616049</v>
       </c>
       <c r="B48" t="n">
-        <v>83315</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5305,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480053</v>
+        <v>480103</v>
       </c>
       <c r="R48" t="n">
-        <v>6992722</v>
+        <v>6992106</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5341,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mer än 10 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,32 +5372,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132616048</v>
+        <v>132616051</v>
       </c>
       <c r="B49" t="n">
-        <v>78345</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5407,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480069</v>
+        <v>479998</v>
       </c>
       <c r="R49" t="n">
-        <v>6992597</v>
+        <v>6992723</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,32 +5469,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132616028</v>
+        <v>132616053</v>
       </c>
       <c r="B50" t="n">
-        <v>83315</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5504,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479938</v>
+        <v>479981</v>
       </c>
       <c r="R50" t="n">
-        <v>6992708</v>
+        <v>6992737</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5552,6 +5540,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2 st plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5578,53 +5571,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132616041</v>
+        <v>132616055</v>
       </c>
       <c r="B51" t="n">
-        <v>57145</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480066</v>
+        <v>480017</v>
       </c>
       <c r="R51" t="n">
-        <v>6992598</v>
+        <v>6992735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5661,7 +5646,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Spillning, tupp</t>
+          <t>6 st små plantor</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5688,32 +5673,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132616084</v>
+        <v>132616057</v>
       </c>
       <c r="B52" t="n">
-        <v>91914</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5723,10 +5708,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480141</v>
+        <v>480029</v>
       </c>
       <c r="R52" t="n">
-        <v>6992268</v>
+        <v>6992701</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,6 +5744,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5785,32 +5775,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132616045</v>
+        <v>132616060</v>
       </c>
       <c r="B53" t="n">
-        <v>80467</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5820,10 +5810,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480012</v>
+        <v>480016</v>
       </c>
       <c r="R53" t="n">
-        <v>6992800</v>
+        <v>6992696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5856,6 +5846,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 20 st plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5882,10 +5877,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132616053</v>
+        <v>132616065</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5917,10 +5912,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479981</v>
+        <v>480053</v>
       </c>
       <c r="R54" t="n">
-        <v>6992737</v>
+        <v>6992856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5957,7 +5952,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2 st plantor</t>
+          <t>Ca 20 st</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5984,32 +5979,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132616030</v>
+        <v>132616071</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6019,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480166</v>
+        <v>479988</v>
       </c>
       <c r="R55" t="n">
-        <v>6992072</v>
+        <v>6992733</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6055,6 +6050,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10-20 plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6081,10 +6081,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132616071</v>
+        <v>132616072</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479988</v>
+        <v>480002</v>
       </c>
       <c r="R56" t="n">
-        <v>6992733</v>
+        <v>6992732</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>10-20 plantor</t>
+          <t>50-100 plantor utspridda kluster</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,32 +6183,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132616038</v>
+        <v>132616074</v>
       </c>
       <c r="B57" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480165</v>
+        <v>479936</v>
       </c>
       <c r="R57" t="n">
-        <v>6992129</v>
+        <v>6992687</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6285,32 +6285,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132616037</v>
+        <v>132616076</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480166</v>
+        <v>479893</v>
       </c>
       <c r="R58" t="n">
-        <v>6992073</v>
+        <v>6992754</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Över 50 plantor, utspritt i kluster</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6384,6 +6384,409 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132616078</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>479874</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6992752</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4 st plantor</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132616080</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>479874</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6992806</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Över 20 plantor, utspritt</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132616082</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>479888</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6992802</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Över 50 plantor, utspritt</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132616048</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>480069</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6992597</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10056-2026 artfynd.xlsx
+++ b/artfynd/A 10056-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616090</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050893</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616030</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616031</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616034</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616035</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616036</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050923</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050924</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050925</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050927</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616088</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616089</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616028</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616029</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050917</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616044</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616045</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616046</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3015,6 +3135,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050898</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050899</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050900</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3321,6 +3456,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050901</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050902</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3525,6 +3670,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050903</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3627,6 +3777,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050904</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3729,6 +3884,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050905</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3831,6 +3991,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050906</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3933,6 +4098,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050907</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4035,6 +4205,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050908</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4137,6 +4312,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050909</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4239,6 +4419,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050911</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4341,6 +4526,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050912</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4443,6 +4633,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050913</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4545,6 +4740,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050914</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4647,6 +4847,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050915</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4749,6 +4954,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4851,6 +5061,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4961,6 +5176,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5063,6 +5283,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050919</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5165,6 +5390,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050920</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5267,6 +5497,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050921</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5369,6 +5604,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616049</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5466,6 +5706,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616051</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5568,6 +5813,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616053</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5670,6 +5920,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616055</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5772,6 +6027,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616057</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5874,6 +6134,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616060</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5976,6 +6241,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616065</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6078,6 +6348,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616071</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6180,6 +6455,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616072</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6282,6 +6562,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616074</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6384,6 +6669,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616076</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6486,6 +6776,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616078</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6588,6 +6883,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616080</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6690,6 +6990,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616082</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6787,8 +7092,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>